--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.70806424648801</v>
+        <v>11.6525604400543</v>
       </c>
       <c r="D2" t="n">
-        <v>27.24002177801233</v>
+        <v>4.426503538927004</v>
       </c>
       <c r="E2" t="n">
-        <v>15.9729470348738</v>
+        <v>2.595603893166992</v>
       </c>
       <c r="F2" t="n">
-        <v>12.78579159848537</v>
+        <v>2.077691134753872</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.17906526890619</v>
+        <v>11.56659810619726</v>
       </c>
       <c r="D3" t="n">
-        <v>45.45451451888677</v>
+        <v>7.386358609319101</v>
       </c>
       <c r="E3" t="n">
-        <v>15.9729470348738</v>
+        <v>2.595603893166992</v>
       </c>
       <c r="F3" t="n">
-        <v>12.78579159848537</v>
+        <v>2.077691134753872</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.08858836471331</v>
+        <v>7.001895609265913</v>
       </c>
       <c r="D4" t="n">
-        <v>25.74425551913748</v>
+        <v>4.183441521859841</v>
       </c>
       <c r="E4" t="n">
-        <v>15.9729470348738</v>
+        <v>2.595603893166992</v>
       </c>
       <c r="F4" t="n">
-        <v>12.78579159848537</v>
+        <v>2.077691134753872</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.43772266109794</v>
+        <v>9.171129932428414</v>
       </c>
       <c r="D5" t="n">
-        <v>46.57000516213124</v>
+        <v>7.567625838846326</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9729470348738</v>
+        <v>2.595603893166992</v>
       </c>
       <c r="F5" t="n">
-        <v>12.78579159848537</v>
+        <v>2.077691134753872</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.75331485293067</v>
+        <v>9.547413663601235</v>
       </c>
       <c r="D6" t="n">
-        <v>59.36309862372679</v>
+        <v>9.646503526355604</v>
       </c>
       <c r="E6" t="n">
-        <v>15.9729470348738</v>
+        <v>2.595603893166992</v>
       </c>
       <c r="F6" t="n">
-        <v>12.78579159848537</v>
+        <v>2.077691134753872</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.13715194243771</v>
+        <v>4.247287190646127</v>
       </c>
       <c r="D7" t="n">
-        <v>26.55829381796847</v>
+        <v>4.315722745419876</v>
       </c>
       <c r="E7" t="n">
-        <v>15.9729470348738</v>
+        <v>2.595603893166992</v>
       </c>
       <c r="F7" t="n">
-        <v>12.78579159848537</v>
+        <v>2.077691134753872</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
